--- a/TP files/TP Sizing Rules ext.xlsx
+++ b/TP files/TP Sizing Rules ext.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\TP files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A2028FC-0D45-4A54-9E71-B6382BB712C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377080F8-E048-4846-8512-F1282596BF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1D0548A-5F2E-4CED-8714-89F76271ED53}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{C1D0548A-5F2E-4CED-8714-89F76271ED53}"/>
   </bookViews>
   <sheets>
     <sheet name="Subsystem level data" sheetId="1" r:id="rId1"/>
@@ -222,7 +222,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -433,38 +433,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -478,23 +459,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8535,19 +8531,19 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="12">
         <v>25626825</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="12">
         <v>41640875</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="12">
         <v>55307461</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="12">
         <v>67645800</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="13">
         <v>79100988</v>
       </c>
     </row>
@@ -8555,19 +8551,19 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="8">
         <v>8093211</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>15139995</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="8">
         <v>21875672</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="8">
         <v>28421847</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="9">
         <v>34858619</v>
       </c>
     </row>
@@ -8575,19 +8571,19 @@
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="8">
         <v>100</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>200</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="8">
         <v>300</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="8">
         <v>400</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="9">
         <v>500</v>
       </c>
     </row>
@@ -8595,41 +8591,41 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="6"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="12">
         <v>21418809</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="12">
         <v>34794958</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="12">
         <v>46225789</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="12">
         <v>56538131.641367003</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="13">
         <v>66112351.669859</v>
       </c>
     </row>
@@ -8637,19 +8633,19 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="8">
         <v>15849994</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>29701618</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="8">
         <v>43537738</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>57142843.174974002</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="9">
         <v>70594792.081210002</v>
       </c>
     </row>
@@ -8657,19 +8653,19 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="8">
         <v>100</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>200</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="8">
         <v>300</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>400</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="9">
         <v>500</v>
       </c>
     </row>
@@ -8677,13 +8673,13 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
@@ -8695,19 +8691,19 @@
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="12">
         <v>22406281.668520998</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="12">
         <v>36407836.716948003</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="12">
         <v>48356933.871104002</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="12">
         <v>59158883.194568001</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="13">
         <v>69160317.103299007</v>
       </c>
     </row>
@@ -8715,19 +8711,19 @@
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="8">
         <v>10119666.936223</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>19112371.345357999</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="8">
         <v>27768464.922476999</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="8">
         <v>36229331.947820999</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="9">
         <v>44555149.351457998</v>
       </c>
     </row>
@@ -8735,19 +8731,19 @@
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="8">
         <v>100</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>200</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="8">
         <v>300</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="8">
         <v>400</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="9">
         <v>500</v>
       </c>
     </row>
@@ -8755,41 +8751,41 @@
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="16"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="12">
         <v>7669432.1445490001</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="12">
         <v>12462012.748919001</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="12">
         <v>16552060.785303</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="12">
         <v>20244599.437461998</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="13">
         <v>23672830.612397</v>
       </c>
     </row>
@@ -8797,19 +8793,19 @@
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="8">
         <v>2532354.7340779998</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>4824783.5055839997</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="8">
         <v>7039092.2815049998</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="8">
         <v>9210067.2764570005</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="9">
         <v>11349670.113733999</v>
       </c>
     </row>
@@ -8817,19 +8813,19 @@
       <c r="A19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="8">
         <v>100</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>200</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="8">
         <v>300</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="8">
         <v>400</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="9">
         <v>500</v>
       </c>
     </row>
@@ -8837,41 +8833,41 @@
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="24"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="12">
         <v>5810725.034217</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="12">
         <v>9441809.8526900001</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="12">
         <v>12540623.553652</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="12">
         <v>15338265.357573999</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="13">
         <v>17931361.084952999</v>
       </c>
     </row>
@@ -8879,19 +8875,19 @@
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="8">
         <v>1347831.286411</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <v>2550042.6345429998</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="8">
         <v>3706216.6339929998</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="8">
         <v>4833733.7797710001</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="9">
         <v>5941459.0866630003</v>
       </c>
     </row>
@@ -8899,19 +8895,19 @@
       <c r="A24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="8">
         <v>100</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="8">
         <v>200</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="8">
         <v>300</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="8">
         <v>400</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="9">
         <v>500</v>
       </c>
     </row>
@@ -8919,41 +8915,41 @@
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="16"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="10">
         <v>14356068.148080001</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="4">
         <v>23327091.220229</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="4">
         <v>30986895.813111</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="4">
         <v>37904054.907972001</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="5">
         <v>44312135.64858</v>
       </c>
     </row>
@@ -8961,19 +8957,19 @@
       <c r="A28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="11">
         <v>8420469.646368999</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="6">
         <v>16224740.773005001</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="6">
         <v>23838780.041857</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="6">
         <v>31331864.484700002</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="7">
         <v>38749653.241508</v>
       </c>
     </row>
@@ -8981,19 +8977,19 @@
       <c r="A29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="8">
         <v>100</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="8">
         <v>200</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="8">
         <v>300</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <v>400</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="9">
         <v>500</v>
       </c>
     </row>
@@ -9001,13 +8997,13 @@
       <c r="A30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="16"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -9016,19 +9012,19 @@
       <c r="B32" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="6">
         <v>6967973.1550240004</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="6">
         <v>11322217.087631</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="6">
         <v>15038182.774700001</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="6">
         <v>18397401.857716002</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="6">
         <v>21507676.914246999</v>
       </c>
     </row>
@@ -9036,28 +9032,28 @@
       <c r="B33" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="6">
         <v>2602992.9140869998</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="6">
         <v>4972078.0409049997</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="6">
         <v>7267189.2779550003</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="6">
         <v>9518894.9176139999</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="6">
         <v>11736913.881987</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -9066,19 +9062,19 @@
       <c r="B35" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="6">
         <v>7388094.9930560002</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="6">
         <v>12004874.132598</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="6">
         <v>15948713.038411001</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="6">
         <v>19506653.050255999</v>
       </c>
-      <c r="G35" s="13">
+      <c r="G35" s="6">
         <v>22804458.734333001</v>
       </c>
     </row>
@@ -9086,30 +9082,30 @@
       <c r="B36" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="6">
         <v>5817476.7322819997</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="6">
         <v>11252662.732100001</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="6">
         <v>16571590.763901999</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="6">
         <v>21812969.567086</v>
       </c>
-      <c r="G36" s="13">
+      <c r="G36" s="6">
         <v>27012739.359521002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B30:F30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9134,7 +9130,7 @@
       <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -9142,10 +9138,10 @@
       <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="16">
         <v>323826266.49213701</v>
       </c>
     </row>
@@ -9153,7 +9149,7 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="6">
         <v>52492736.340538003</v>
       </c>
     </row>
@@ -9161,7 +9157,7 @@
       <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="6">
         <v>44699222.912067004</v>
       </c>
     </row>
@@ -9169,7 +9165,7 @@
       <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="6">
         <v>45728766.068461001</v>
       </c>
     </row>
@@ -9177,7 +9173,7 @@
       <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="6">
         <v>38523043.390362002</v>
       </c>
     </row>
@@ -9185,91 +9181,91 @@
       <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="6">
         <v>14854413.191059001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="6">
         <v>114483068.90414201</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
-      <c r="C10" s="13">
+      <c r="B10" s="28"/>
+      <c r="C10" s="6">
         <v>42844783.975001</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="23"/>
-      <c r="C11" s="13">
+      <c r="B11" s="28"/>
+      <c r="C11" s="6">
         <v>65388181.744566999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="13"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="26" t="s">
+      <c r="I15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="26" t="s">
+      <c r="J15" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="6">
         <v>323826266.49213701</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="8">
         <v>60848228.412312001</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="8">
         <v>66679856.177337997</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="8">
         <v>131908373.182464</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="8">
         <v>0</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="8">
         <v>0</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="8">
         <v>14557698.932056</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="8">
         <v>45487946.177661002</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="8">
         <v>4344163.6103069996</v>
       </c>
     </row>
@@ -9277,27 +9273,27 @@
       <c r="A17" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="6">
         <v>52492736.340538003</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8">
         <v>38713366.209073998</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="8">
         <v>0</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="8">
         <v>0</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="8">
         <v>4159375.8496750002</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="8">
         <v>7879742.7365960004</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="8">
         <v>1740251.545194</v>
       </c>
     </row>
@@ -9305,27 +9301,27 @@
       <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="6">
         <v>44699222.912067004</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8">
         <v>25316872.197951999</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="8">
         <v>0</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="8">
         <v>0</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="8">
         <v>4091403.9198949998</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="8">
         <v>14354331.935678</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="8">
         <v>936614.85854199994</v>
       </c>
     </row>
@@ -9333,27 +9329,27 @@
       <c r="A19" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="6">
         <v>45728766.068461001</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22">
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8">
         <v>30547682.305610001</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="8">
         <v>0</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="8">
         <v>0</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="8">
         <v>3809751.7790930001</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="8">
         <v>9846056.7666989993</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19" s="8">
         <v>1525275.2170599999</v>
       </c>
     </row>
@@ -9361,27 +9357,27 @@
       <c r="A20" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="6">
         <v>38523043.390362002</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8">
         <v>25795240.851413999</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="8">
         <v>0</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="8">
         <v>0</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="8">
         <v>1955864.4198720001</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="8">
         <v>10669848.419475</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="8">
         <v>102089.699603</v>
       </c>
     </row>
@@ -9389,85 +9385,85 @@
       <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="6">
         <v>14854413.191059001</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8">
         <v>11535211.618414</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="8">
         <v>0</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="8">
         <v>0</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="8">
         <v>541302.96352300001</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="8">
         <v>2737966.3192130001</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="8">
         <v>39932.289908999999</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="6">
         <v>114483068.90414201</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="8">
         <v>56943403.380039997</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="8">
         <v>57539665.524102002</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="13">
+      <c r="A23" s="28"/>
+      <c r="B23" s="6">
         <v>42844783.975001</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="8">
         <v>26951823.879365999</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="8">
         <v>15892960.095635001</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="13">
+      <c r="A24" s="28"/>
+      <c r="B24" s="6">
         <v>65388181.744566999</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="8">
         <v>28583709.196743999</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="8">
         <v>36804472.547822997</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -9478,39 +9474,39 @@
       <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="18">
         <f>(B16-SUM(B17:B22))/SUM(B17:B22)</f>
         <v>4.1974912101839575E-2</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="18">
         <f>(C16-SUM(C17:C22))/SUM(C17:C22)</f>
         <v>6.8573790825448566E-2</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="18">
         <f>(D16-SUM(D17:D22))/SUM(D17:D22)</f>
         <v>0.15885025694852858</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="18">
         <f t="shared" ref="E28:J28" si="0">(E16-SUM(E17:E22))/SUM(E17:E22)</f>
         <v>1.1296599930950122E-16</v>
       </c>
-      <c r="F28" s="27" t="e">
+      <c r="F28" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G28" s="27" t="e">
+      <c r="G28" s="18" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="18">
         <f t="shared" si="0"/>
         <v>-1.3754533218253677E-13</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="18">
         <f t="shared" si="0"/>
         <v>-2.3003487257966278E-13</v>
       </c>
@@ -9519,24 +9515,24 @@
       <c r="A29" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="18">
         <f>(B22-SUM(B23:B24))/SUM(B23:B24)</f>
         <v>5.7746760823019924E-2</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="18">
         <f t="shared" ref="C29:D29" si="1">(C22-SUM(C23:C24))/SUM(C23:C24)</f>
         <v>2.5350802017161698E-2</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="18">
         <f t="shared" si="1"/>
         <v>9.1887453292188739E-2</v>
       </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
     </row>
     <row r="33" spans="2:40" x14ac:dyDescent="0.25">
       <c r="I33" t="s">
@@ -9630,19 +9626,19 @@
       </c>
     </row>
     <row r="36" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B36" s="28">
+      <c r="B36" s="19">
         <v>1</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="20">
         <v>323826266.49213701</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="20">
         <v>192756601.594776</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="21">
         <v>131069664.897361</v>
       </c>
       <c r="H36">
@@ -10182,19 +10178,19 @@
       </c>
     </row>
     <row r="42" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B42" s="28">
+      <c r="B42" s="19">
         <v>7</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="20">
         <v>114483068.90414201</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="20">
         <v>56943403.380039997</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="21">
         <v>57539665.524102002</v>
       </c>
       <c r="H42">
@@ -10458,75 +10454,75 @@
       </c>
     </row>
     <row r="46" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="D46" s="27">
+      <c r="D46" s="18">
         <f>(D36-SUM(D37:D42))/SUM(D37:D42)</f>
         <v>4.1974912101839575E-2</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="18">
         <f t="shared" ref="E46:F46" si="2">(E36-SUM(E37:E42))/SUM(E37:E42)</f>
         <v>2.0676665601711386E-2</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="18">
         <f t="shared" si="2"/>
         <v>7.4962930086408835E-2</v>
       </c>
-      <c r="J46" s="27">
+      <c r="J46" s="18">
         <f>(J36-SUM(J37:J42))/SUM(J37:J42)</f>
         <v>4.0436387047869372E-2</v>
       </c>
-      <c r="K46" s="27">
+      <c r="K46" s="18">
         <f t="shared" ref="K46:L46" si="3">(K36-SUM(K37:K42))/SUM(K37:K42)</f>
         <v>1.9633307520004015E-2</v>
       </c>
-      <c r="L46" s="27">
+      <c r="L46" s="18">
         <f t="shared" si="3"/>
         <v>7.1891599419648303E-2</v>
       </c>
-      <c r="Q46" s="27">
+      <c r="Q46" s="18">
         <f>(Q36-SUM(Q37:Q42))/SUM(Q37:Q42)</f>
         <v>4.2338974648645736E-2</v>
       </c>
-      <c r="R46" s="27">
+      <c r="R46" s="18">
         <f t="shared" ref="R46:S46" si="4">(R36-SUM(R37:R42))/SUM(R37:R42)</f>
         <v>2.0911118468109807E-2</v>
       </c>
-      <c r="S46" s="27">
+      <c r="S46" s="18">
         <f t="shared" si="4"/>
         <v>7.5670271937754607E-2</v>
       </c>
-      <c r="X46" s="27">
+      <c r="X46" s="18">
         <f>(X36-SUM(X37:X42))/SUM(X37:X42)</f>
         <v>4.406119843507636E-2</v>
       </c>
-      <c r="Y46" s="27">
+      <c r="Y46" s="18">
         <f t="shared" ref="Y46:Z46" si="5">(Y36-SUM(Y37:Y42))/SUM(Y37:Y42)</f>
         <v>2.198055038889404E-2</v>
       </c>
-      <c r="Z46" s="27">
+      <c r="Z46" s="18">
         <f t="shared" si="5"/>
         <v>7.8949496247975218E-2</v>
       </c>
-      <c r="AE46" s="27">
+      <c r="AE46" s="18">
         <f>(AE36-SUM(AE37:AE42))/SUM(AE37:AE42)</f>
         <v>4.5599082990203738E-2</v>
       </c>
-      <c r="AF46" s="27">
+      <c r="AF46" s="18">
         <f t="shared" ref="AF46:AG46" si="6">(AF36-SUM(AF37:AF42))/SUM(AF37:AF42)</f>
         <v>2.2893713997628171E-2</v>
       </c>
-      <c r="AG46" s="27">
+      <c r="AG46" s="18">
         <f t="shared" si="6"/>
         <v>8.1806157947254973E-2</v>
       </c>
-      <c r="AL46" s="27">
+      <c r="AL46" s="18">
         <f>(AL36-SUM(AL37:AL42))/SUM(AL37:AL42)</f>
         <v>4.6994408271437756E-2</v>
       </c>
-      <c r="AM46" s="27">
+      <c r="AM46" s="18">
         <f t="shared" ref="AM46:AN46" si="7">(AM36-SUM(AM37:AM42))/SUM(AM37:AM42)</f>
         <v>2.3686186516959987E-2</v>
       </c>
-      <c r="AN46" s="27">
+      <c r="AN46" s="18">
         <f t="shared" si="7"/>
         <v>8.435690347111921E-2</v>
       </c>
@@ -10707,15 +10703,15 @@
       </c>
     </row>
     <row r="62" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="K62" s="27">
+      <c r="K62" s="18">
         <f>(K52-SUM(K53:K58))/SUM(K53:K58)</f>
         <v>4.0735621993855033E-2</v>
       </c>
-      <c r="L62" s="27">
+      <c r="L62" s="18">
         <f t="shared" ref="L62:M62" si="8">(L52-SUM(L53:L58))/SUM(L53:L58)</f>
         <v>1.9704485092038933E-2</v>
       </c>
-      <c r="M62" s="27">
+      <c r="M62" s="18">
         <f t="shared" si="8"/>
         <v>7.2524410324330157E-2</v>
       </c>
@@ -10896,15 +10892,15 @@
       </c>
     </row>
     <row r="77" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="K77" s="27">
+      <c r="K77" s="18">
         <f>(K67-SUM(K68:K73))/SUM(K68:K73)</f>
         <v>4.1014015469078825E-2</v>
       </c>
-      <c r="L77" s="27">
+      <c r="L77" s="18">
         <f t="shared" ref="L77:M77" si="9">(L67-SUM(L68:L73))/SUM(L68:L73)</f>
         <v>1.9774444924682652E-2</v>
       </c>
-      <c r="M77" s="27">
+      <c r="M77" s="18">
         <f t="shared" si="9"/>
         <v>7.3088304809822355E-2</v>
       </c>
@@ -10954,16 +10950,16 @@
       <c r="B2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="8">
         <v>1197292009.04357</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="8">
         <v>185462390.76504701</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="8">
         <v>233233730.09886</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="8">
         <v>778595888.17966199</v>
       </c>
     </row>
@@ -10974,16 +10970,16 @@
       <c r="B3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="8">
         <v>314696120.86390698</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="8">
         <v>185462390.76504701</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="8">
         <v>129233730.09886</v>
       </c>
-      <c r="F3" s="22"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -10992,16 +10988,16 @@
       <c r="B4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="8">
         <v>37000000</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="8">
         <v>0</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="8">
         <v>37000000</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11012,16 +11008,16 @@
       <c r="B5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="8">
         <v>67000000</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="8">
         <v>0</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="8">
         <v>67000000</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="8">
         <v>0</v>
       </c>
     </row>
@@ -11032,16 +11028,16 @@
       <c r="B6" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="8">
         <v>778595888.17966199</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="8">
         <v>0</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="8">
         <v>0</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="8">
         <v>778595888.17966199</v>
       </c>
     </row>

--- a/TP files/TP Sizing Rules ext.xlsx
+++ b/TP files/TP Sizing Rules ext.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\TP files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377080F8-E048-4846-8512-F1282596BF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D564CA6-EC6B-400D-BA7E-48BA7771AD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{C1D0548A-5F2E-4CED-8714-89F76271ED53}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1D0548A-5F2E-4CED-8714-89F76271ED53}"/>
   </bookViews>
   <sheets>
     <sheet name="Subsystem level data" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -470,6 +470,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -479,17 +488,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2762,7 +2768,7 @@
             <c:numRef>
               <c:f>'Subsystem level data'!$B$18:$F$18</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>2532354.7340779998</c:v>
@@ -2976,7 +2982,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="fr-FR"/>
-                  <a:t>Mass</a:t>
+                  <a:t>Mass [kg]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3093,7 +3099,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="fr-FR"/>
-                  <a:t>Costs</a:t>
+                  <a:t>Costs [€]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -3127,7 +3133,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8084,16 +8090,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>748392</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>126711</xdr:colOff>
+      <xdr:colOff>113103</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>67932</xdr:rowOff>
+      <xdr:rowOff>27110</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8591,13 +8597,13 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -8673,13 +8679,13 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
@@ -8751,13 +8757,13 @@
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -8793,19 +8799,19 @@
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="29">
         <v>2532354.7340779998</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="29">
         <v>4824783.5055839997</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="29">
         <v>7039092.2815049998</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="29">
         <v>9210067.2764570005</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="30">
         <v>11349670.113733999</v>
       </c>
     </row>
@@ -8833,13 +8839,13 @@
       <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="24"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="27"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
@@ -8915,13 +8921,13 @@
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="27"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
@@ -8997,13 +9003,13 @@
       <c r="A30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="27"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
